--- a/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_meredithBehavioralModelsParkinsons2006.xlsx
+++ b/03_IE_tasks/data/related/outcomes_endpoints/Endpoints_meredithBehavioralModelsParkinsons2006.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/sdoneva/Documents/Work/In Progress/PhD/PhD Projects/In Progress/Preclinical_Pipeline/03_IE_tasks/data/related/outcomes_endpoints/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{5C3706DB-D4FE-D14B-848D-B50D6E16C0D5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DCC80ED-1BDA-4D4D-B1EA-F2EEDD7FC44C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32260" yWindow="2620" windowWidth="27640" windowHeight="16940" xr2:uid="{0E65B27B-7837-D449-9E05-E6D5C41429BE}"/>
+    <workbookView xWindow="47080" yWindow="3420" windowWidth="27640" windowHeight="16940" xr2:uid="{0E65B27B-7837-D449-9E05-E6D5C41429BE}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -116,10 +116,10 @@
     <t>Latency to contact and latency to remove adhesive label on snout (max 60 s)</t>
   </si>
   <si>
-    <t>Bin‐cotton Use</t>
-  </si>
-  <si>
     <t>Time (and/or amount) to shred pre-weighed cotton over 72 h</t>
+  </si>
+  <si>
+    <t>Bin‐cotton use</t>
   </si>
 </sst>
 </file>
@@ -502,6 +502,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4C7A30D9-3B1A-0742-9095-74E409179BC6}">
   <dimension ref="A1:C13"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <cols>
+    <col min="1" max="1" width="34" customWidth="1"/>
+  </cols>
   <sheetData>
     <row r="1" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A1" s="1" t="s">
@@ -637,10 +640,10 @@
     </row>
     <row r="13" spans="1:3" x14ac:dyDescent="0.2">
       <c r="A13" t="s">
+        <v>27</v>
+      </c>
+      <c r="B13" t="s">
         <v>26</v>
-      </c>
-      <c r="B13" t="s">
-        <v>27</v>
       </c>
       <c r="C13" t="s">
         <v>5</v>
